--- a/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,90 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>BENY ALEXANDER</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
   </si>
 </sst>
 </file>
@@ -471,16 +555,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.88</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -494,16 +581,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -517,16 +607,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>48.48</v>
+      </c>
+      <c r="H4">
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +675,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -605,7 +698,7 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -628,7 +721,7 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -687,16 +780,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.88</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,16 +806,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -733,16 +832,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>48.48</v>
+      </c>
+      <c r="H4">
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -752,7 +854,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -782,6 +884,236 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920021</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920034</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920040</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920107</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920109</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920112</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920014</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -73,15 +73,30 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>AMADOR</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -94,21 +109,36 @@
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>PORRAS</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
@@ -118,24 +148,33 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
   </si>
   <si>
     <t>OCTAVIO</t>
   </si>
   <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
     <t>FRANCISCO ALAN</t>
   </si>
   <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
     <t>SERGIO MARIANO</t>
   </si>
   <si>
@@ -148,13 +187,7 @@
     <t>GUILLERMO</t>
   </si>
   <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
+    <t>ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -854,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -886,16 +919,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920021</v>
+        <v>20330051920034</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -909,22 +942,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920034</v>
+        <v>20330051920044</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -932,16 +965,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920040</v>
+        <v>20330051920102</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -955,114 +988,114 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920101</v>
+        <v>20330051920006</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920107</v>
+        <v>20330051920009</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920109</v>
+        <v>20330051920014</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920112</v>
+        <v>20330051920021</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920006</v>
+        <v>20330051920040</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1070,22 +1103,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920009</v>
+        <v>20330051920096</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1093,24 +1126,116 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920014</v>
+        <v>20330051920101</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920109</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
         <v>35</v>
       </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
@@ -79,27 +79,27 @@
     <t>BERNARDO</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -118,30 +118,30 @@
     <t>CHONCOA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>VALENCIA</t>
   </si>
   <si>
@@ -154,28 +154,28 @@
     <t>URIEL</t>
   </si>
   <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
     <t>IVAN</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
   </si>
   <si>
     <t>ROSA ISELA</t>
@@ -965,7 +965,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920102</v>
+        <v>20330051920006</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -980,18 +980,18 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920006</v>
+        <v>20330051920009</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
         <v>34</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920009</v>
+        <v>20330051920014</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920014</v>
+        <v>20330051920021</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920021</v>
+        <v>20330051920040</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -1072,7 +1072,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920040</v>
+        <v>20330051920096</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920096</v>
+        <v>20330051920101</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920101</v>
+        <v>20330051920102</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -1224,7 +1224,7 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
         <v>56</v>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
@@ -73,21 +73,21 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>AMADOR</t>
   </si>
   <si>
@@ -112,24 +112,24 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>PORRAS</t>
   </si>
   <si>
@@ -148,22 +148,22 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
     <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
   </si>
   <si>
     <t>FRANCISCO ALAN</t>
@@ -919,7 +919,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920034</v>
+        <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -934,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -942,7 +942,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920044</v>
+        <v>20330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -957,18 +957,18 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920006</v>
+        <v>20330051920009</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -988,7 +988,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920009</v>
+        <v>20330051920014</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920014</v>
+        <v>20330051920021</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920021</v>
+        <v>20330051920034</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -1224,7 +1224,7 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
         <v>56</v>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,123 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
-  </si>
-  <si>
-    <t>BENY ALEXANDER</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -588,16 +471,16 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>8.800000000000001</v>
@@ -614,19 +497,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>7</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>78.13</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -705,16 +588,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -728,16 +614,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -751,16 +640,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96.97</v>
+      </c>
+      <c r="H4">
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -813,19 +705,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -839,19 +731,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -868,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>48.48</v>
+        <v>96.97</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -917,328 +809,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920044</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920006</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920009</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920014</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920021</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920034</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920040</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920096</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920101</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920102</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920107</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920109</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920112</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20212.xlsx
@@ -717,7 +717,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -743,7 +743,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>96.97</v>
+        <v>90.91</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
